--- a/fichiers/Synthèse_compétences_BTS_SIO_VAL_ANTHONY.xlsx
+++ b/fichiers/Synthèse_compétences_BTS_SIO_VAL_ANTHONY.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\valan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\valan\Desktop\Portfolio\fichiers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CE35E7-0ACA-457D-8261-27117D876F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3641D3C1-8C2A-4EB9-A138-6DDB13E287DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,9 +99,6 @@
     <t>Réalisations en milieu professionnel en cours de seconde année</t>
   </si>
   <si>
-    <t>Adresse URL du portfolio :</t>
-  </si>
-  <si>
     <t>SESSION 2026</t>
   </si>
   <si>
@@ -168,6 +165,9 @@
   </si>
   <si>
     <t>09/2025 - 06/2026</t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio : https://imskide.github.io/portfolio/</t>
   </si>
 </sst>
 </file>
@@ -705,9 +705,48 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -730,45 +769,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1090,56 +1090,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="26"/>
+    </row>
+    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+    </row>
+    <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="24"/>
-    </row>
-    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-    </row>
-    <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="26"/>
-      <c r="H3" s="32"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="45"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="30"/>
+      <c r="A4" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="43"/>
       <c r="F4" s="12" t="s">
         <v>8</v>
       </c>
@@ -1147,26 +1147,26 @@
         <v>14</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="43" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="45"/>
+      <c r="A5" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="37"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="33" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1189,10 +1189,10 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="34"/>
-      <c r="B7" s="42"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>9</v>
@@ -1246,16 +1246,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="37"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1294,22 +1294,22 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D9" s="22"/>
       <c r="E9" s="22"/>
       <c r="F9" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G9" s="22"/>
       <c r="H9" s="23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -1349,19 +1349,19 @@
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" s="22"/>
       <c r="D10" s="22"/>
       <c r="E10" s="22"/>
       <c r="F10" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H10" s="23"/>
       <c r="I10"/>
@@ -1402,19 +1402,19 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="21" t="s">
         <v>34</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>35</v>
       </c>
       <c r="C11" s="22"/>
       <c r="D11" s="22"/>
       <c r="E11" s="22"/>
       <c r="F11" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H11" s="23"/>
       <c r="I11"/>
@@ -1455,26 +1455,26 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E12" s="22"/>
       <c r="F12" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -1783,16 +1783,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" s="38" t="s">
+      <c r="A19" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="39"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="40"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="32"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1831,15 +1831,15 @@
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" s="22"/>
       <c r="D20" s="22"/>
       <c r="E20" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F20" s="22"/>
       <c r="G20" s="22"/>
@@ -1882,28 +1882,28 @@
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
@@ -2167,16 +2167,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A27" s="38" t="s">
+      <c r="A27" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="B27" s="39"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="39"/>
-      <c r="H27" s="40"/>
+      <c r="B27" s="31"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="32"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2215,26 +2215,26 @@
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G28" s="22"/>
       <c r="H28" s="23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I28"/>
       <c r="J28"/>
@@ -2635,6 +2635,11 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2642,11 +2647,6 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
